--- a/reports/telegram/aegis_usa_2026-09-08.xlsx
+++ b/reports/telegram/aegis_usa_2026-09-08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -527,220 +527,98 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🔎 WHY NEW=0 · 516 scored · 18 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Stop State</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Dist to Stop %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Max Loss if Stop %</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>175.23</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>161.969</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>-7.57</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>204.13</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>375.62</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>369.35</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>356.8957</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>402.23</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -752,7 +630,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -771,13 +649,13 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>193.17</v>
+        <v>175.23</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>186.42</v>
+        <v>174.33</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-3.49</v>
+        <v>-0.51</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -785,7 +663,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>174.3364</v>
+        <v>161.969</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -793,17 +671,17 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.48</v>
+        <v>7.09</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-9.75</v>
+        <v>-7.57</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>227.43</v>
+        <v>204.13</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-IT-20260810-b5fd37</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -820,12 +698,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -835,17 +713,17 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.83</v>
+        <v>375.62</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>4.68</v>
+        <v>369.35</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -853,7 +731,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>60.0271</v>
+        <v>356.8957</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -861,22 +739,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.17</v>
+        <v>3.37</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.96</v>
+        <v>-4.98</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>69.53</v>
+        <v>402.23</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -888,12 +766,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -903,17 +781,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>275.17</v>
+        <v>193.17</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>277.03</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.68</v>
+        <v>186.42</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -921,7 +799,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>261.9314</v>
+        <v>174.3364</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -929,22 +807,22 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.45</v>
+        <v>6.48</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.81</v>
+        <v>-9.75</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>295.03</v>
+        <v>227.43</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R2-IT-20260810-b5fd37</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -956,7 +834,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -971,17 +849,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>175.23</v>
+        <v>63.83</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>-0.51</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>4.68</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -989,7 +867,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>155.965</v>
+        <v>60.0271</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -997,17 +875,17 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>10.53</v>
+        <v>10.17</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-10.99</v>
+        <v>-5.96</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>204.13</v>
+        <v>69.53</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1024,7 +902,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1039,17 +917,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>505.11</v>
+        <v>275.17</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>499.7</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>-1.07</v>
+        <v>277.03</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.68</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1057,7 +935,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>469.0698</v>
+        <v>261.9314</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1065,17 +943,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.13</v>
+        <v>5.45</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-7.13</v>
+        <v>-4.81</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>559.17</v>
+        <v>295.03</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1092,7 +970,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1111,13 +989,13 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>272.96</v>
+        <v>175.23</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>266.51</v>
+        <v>174.33</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-2.36</v>
+        <v>-0.51</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1125,7 +1003,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>247.1386</v>
+        <v>155.965</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1133,17 +1011,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.27</v>
+        <v>10.53</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.99</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>311.69</v>
+        <v>204.13</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1160,7 +1038,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1175,17 +1053,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>90.22</v>
+        <v>505.11</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>499.7</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-2.57</v>
+        <v>-1.07</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1193,7 +1071,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>84.9543</v>
+        <v>469.0698</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1201,17 +1079,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.35</v>
+        <v>6.13</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-5.84</v>
+        <v>-7.13</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>98.12</v>
+        <v>559.17</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-DXCM-20260820-a0e45f</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1228,7 +1106,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1247,13 +1125,13 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>78.03</v>
+        <v>272.96</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>266.51</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2.91</v>
+        <v>-2.36</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1139,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>72.40940000000001</v>
+        <v>247.1386</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1269,17 +1147,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.42</v>
+        <v>7.27</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.2</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>311.69</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-UBER-20260810-3f4c24</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1296,7 +1174,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1311,17 +1189,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>193.17</v>
+        <v>90.22</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>186.42</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-3.49</v>
+        <v>-2.57</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1207,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>170.3286</v>
+        <v>84.9543</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1337,17 +1215,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.630000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-11.82</v>
+        <v>-5.84</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>227.43</v>
+        <v>98.12</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-IT-20260810-04dfbc</t>
+          <t>USA-R1-DXCM-20260820-a0e45f</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1364,32 +1242,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>63.61</v>
+        <v>78.03</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>5.05</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.91</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1397,7 +1275,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>63.8043</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1405,22 +1283,22 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.51</v>
+        <v>4.42</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.31</v>
+        <v>-7.2</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>69.45</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R1-UBER-20260810-3f4c24</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1432,17 +1310,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1451,13 +1329,13 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>360.65</v>
+        <v>193.17</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>375.07</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>4</v>
+        <v>186.42</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1465,7 +1343,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>362.4986</v>
+        <v>170.3286</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1473,22 +1351,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.51</v>
+        <v>-11.82</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>384</v>
+        <v>227.43</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R1-IT-20260810-04dfbc</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1378,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1519,13 +1397,13 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>89.53</v>
+        <v>63.61</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>-1.82</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>5.05</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1533,7 +1411,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>83.2157</v>
+        <v>63.8043</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1541,17 +1419,17 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.33</v>
+        <v>4.51</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.05</v>
+        <v>0.31</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>99.06</v>
+        <v>69.45</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1568,12 +1446,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1583,17 +1461,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>196.21</v>
+        <v>360.65</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>259.23</v>
+        <v>375.07</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>32.12</v>
+        <v>4</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1601,7 +1479,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>179.3029</v>
+        <v>362.4986</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1609,22 +1487,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>30.83</v>
+        <v>3.35</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.619999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>221.57</v>
+        <v>384</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1514,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1651,17 +1529,17 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>103.51</v>
+        <v>89.53</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>122.11</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>17.97</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-1.82</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1669,7 +1547,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>91.0157</v>
+        <v>83.2157</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1677,22 +1555,22 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>25.46</v>
+        <v>5.33</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-12.07</v>
+        <v>-7.05</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>122.25</v>
+        <v>99.06</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1582,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1719,17 +1597,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>361.99</v>
+        <v>196.21</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>370.72</v>
+        <v>259.23</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2.41</v>
+        <v>32.12</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1737,7 +1615,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>342.2271</v>
+        <v>179.3029</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1745,17 +1623,17 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7.69</v>
+        <v>30.83</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.46</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>391.63</v>
+        <v>221.57</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -1772,7 +1650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1791,13 +1669,13 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>187.7</v>
+        <v>103.51</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>188.8</v>
+        <v>122.11</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.59</v>
+        <v>17.97</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -1805,7 +1683,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>180.8543</v>
+        <v>91.0157</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1813,17 +1691,17 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.21</v>
+        <v>25.46</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.65</v>
+        <v>-12.07</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>197.97</v>
+        <v>122.25</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -1840,7 +1718,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1855,17 +1733,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>126.68</v>
+        <v>361.99</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>126.75</v>
+        <v>370.72</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.06</v>
+        <v>2.41</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -1873,7 +1751,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>119.43</v>
+        <v>342.2271</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1881,17 +1759,17 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.78</v>
+        <v>7.69</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.46</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>137.55</v>
+        <v>391.63</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1908,7 +1786,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1923,17 +1801,17 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>344.5</v>
+        <v>187.7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>338.46</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-1.75</v>
+        <v>188.8</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.59</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -1941,7 +1819,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>323.138</v>
+        <v>180.8543</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1949,17 +1827,17 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.2</v>
+        <v>-3.65</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>376.54</v>
+        <v>197.97</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1976,7 +1854,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1991,17 +1869,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>60.09</v>
+        <v>126.68</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>-2.78</v>
+        <v>126.75</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.06</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -2009,7 +1887,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>56.6217</v>
+        <v>119.43</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -2017,17 +1895,17 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.08</v>
+        <v>5.78</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.78</v>
+        <v>-5.72</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>65.3</v>
+        <v>137.55</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -2044,143 +1922,289 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>323.138</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>56.6217</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <v>161.85</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>156.29</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>-3.44</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="n">
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>147.9529</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>-8.59</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>182.7</v>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
           <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
+    <mergeCell ref="A5:P5"/>
     <mergeCell ref="A32:P32"/>
     <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A39:P39"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A30:P30"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="A33:P33"/>
-    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_usa_2026-09-08.xlsx
+++ b/reports/telegram/aegis_usa_2026-09-08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22 investable · NEW 0 · ACTIVE+ 11 · ACTIVE 11   ·   R2 6 · MOMENTUM 0 · R1 16 (advisory)</t>
+          <t>24 investable · NEW 2 · ACTIVE+ 11 · ACTIVE 11   ·   R2 8 · MOMENTUM 0 · R1 16 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 22 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.72% from entry, worst single -12.07%</t>
+          <t>🛡 DOWNSIDE · 24 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.73% from entry, worst single -12.07%</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 516 scored · 18 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+          <t>🔎 NEW=2 · 516 scored · 19 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>175.23</v>
+        <v>39.59</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>-0.51</v>
+        <v>39.59</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>161.969</v>
+        <v>36.245</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.57</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>204.13</v>
+        <v>46.28</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
+          <t>USA-R2-SMCI-20260908-c2c66b</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>375.62</v>
+        <v>370.72</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>369.35</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>-1.67</v>
+        <v>370.72</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>356.8957</v>
+        <v>350.9043</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.37</v>
+        <v>5.35</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.98</v>
+        <v>-5.35</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>402.23</v>
+        <v>400.44</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
+          <t>USA-R2-VLO-20260908-e69cee</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>193.17</v>
+        <v>175.23</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>186.42</v>
+        <v>174.33</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-3.49</v>
+        <v>-0.51</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>174.3364</v>
+        <v>161.969</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.48</v>
+        <v>7.09</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-9.75</v>
+        <v>-7.57</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>227.43</v>
+        <v>204.13</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-IT-20260810-b5fd37</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.83</v>
+        <v>375.62</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>4.68</v>
+        <v>369.35</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>60.0271</v>
+        <v>356.8957</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>10.17</v>
+        <v>3.37</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.96</v>
+        <v>-4.98</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>69.53</v>
+        <v>402.23</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>275.17</v>
+        <v>193.17</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>277.03</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.68</v>
+        <v>186.42</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>261.9314</v>
+        <v>174.3364</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.45</v>
+        <v>6.48</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.81</v>
+        <v>-9.75</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>295.03</v>
+        <v>227.43</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R2-IT-20260810-b5fd37</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>175.23</v>
+        <v>63.83</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-0.51</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4.68</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>155.965</v>
+        <v>60.0271</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.53</v>
+        <v>10.17</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-10.99</v>
+        <v>-5.96</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>204.13</v>
+        <v>69.53</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>505.11</v>
+        <v>275.17</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>499.7</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-1.07</v>
+        <v>277.03</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.68</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>469.0698</v>
+        <v>261.9314</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1079,17 +1079,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.13</v>
+        <v>5.45</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.13</v>
+        <v>-4.81</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>559.17</v>
+        <v>295.03</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>272.96</v>
+        <v>175.23</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>266.51</v>
+        <v>174.33</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2.36</v>
+        <v>-0.51</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>247.1386</v>
+        <v>155.965</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1147,17 +1147,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.27</v>
+        <v>10.53</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.99</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>311.69</v>
+        <v>204.13</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>90.22</v>
+        <v>505.11</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>499.7</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-2.57</v>
+        <v>-1.07</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>84.9543</v>
+        <v>469.0698</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1215,17 +1215,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.35</v>
+        <v>6.13</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.84</v>
+        <v>-7.13</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>98.12</v>
+        <v>559.17</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-DXCM-20260820-a0e45f</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>78.03</v>
+        <v>272.96</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>266.51</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-2.91</v>
+        <v>-2.36</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>72.40940000000001</v>
+        <v>247.1386</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1283,17 +1283,17 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.42</v>
+        <v>7.27</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-7.2</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>311.69</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-UBER-20260810-3f4c24</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>193.17</v>
+        <v>90.22</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>186.42</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-3.49</v>
+        <v>-2.57</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>170.3286</v>
+        <v>84.9543</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>8.630000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-11.82</v>
+        <v>-5.84</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>227.43</v>
+        <v>98.12</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-IT-20260810-04dfbc</t>
+          <t>USA-R1-DXCM-20260820-a0e45f</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>63.61</v>
+        <v>78.03</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>5.05</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-2.91</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>63.8043</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.51</v>
+        <v>4.42</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.31</v>
+        <v>-7.2</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>69.45</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R1-UBER-20260810-3f4c24</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>360.65</v>
+        <v>193.17</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>375.07</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>4</v>
+        <v>186.42</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>362.4986</v>
+        <v>170.3286</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1487,22 +1487,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.51</v>
+        <v>-11.82</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>384</v>
+        <v>227.43</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R1-IT-20260810-04dfbc</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>89.53</v>
+        <v>63.61</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-1.82</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>5.05</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>83.2157</v>
+        <v>63.8043</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1555,17 +1555,17 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.33</v>
+        <v>4.51</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.05</v>
+        <v>0.31</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>99.06</v>
+        <v>69.45</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>196.21</v>
+        <v>360.65</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>259.23</v>
+        <v>375.07</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>32.12</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>179.3029</v>
+        <v>362.4986</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>30.83</v>
+        <v>3.35</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.619999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>221.57</v>
+        <v>384</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>103.51</v>
+        <v>89.53</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>122.11</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>17.97</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.82</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>91.0157</v>
+        <v>83.2157</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>25.46</v>
+        <v>5.33</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.07</v>
+        <v>-7.05</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>122.25</v>
+        <v>99.06</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>361.99</v>
+        <v>196.21</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>370.72</v>
+        <v>259.23</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2.41</v>
+        <v>32.12</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>342.2271</v>
+        <v>179.3029</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1759,17 +1759,17 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.69</v>
+        <v>30.83</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.46</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>391.63</v>
+        <v>221.57</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>187.7</v>
+        <v>103.51</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>188.8</v>
+        <v>122.11</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.59</v>
+        <v>17.97</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>180.8543</v>
+        <v>91.0157</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.21</v>
+        <v>25.46</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.65</v>
+        <v>-12.07</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>197.97</v>
+        <v>122.25</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>126.68</v>
+        <v>361.99</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>126.75</v>
+        <v>370.72</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.06</v>
+        <v>2.41</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>119.43</v>
+        <v>342.2271</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1895,17 +1895,17 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.78</v>
+        <v>7.69</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.46</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>137.55</v>
+        <v>391.63</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>344.5</v>
+        <v>187.7</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>338.46</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-1.75</v>
+        <v>188.8</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.59</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>323.138</v>
+        <v>180.8543</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -1963,17 +1963,17 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-6.2</v>
+        <v>-3.65</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>376.54</v>
+        <v>197.97</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>60.09</v>
+        <v>126.68</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-2.78</v>
+        <v>126.75</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.06</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>56.6217</v>
+        <v>119.43</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
@@ -2031,17 +2031,17 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.08</v>
+        <v>5.78</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.78</v>
+        <v>-5.72</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>65.3</v>
+        <v>137.55</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2058,131 +2058,267 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>323.138</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>56.6217</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>161.85</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>156.29</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>-3.44</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="n">
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>147.9529</v>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>-8.59</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>182.7</v>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -2191,7 +2327,7 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A42:P42"/>
     <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A37:P37"/>
@@ -2203,7 +2339,7 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A33:P33"/>
+    <mergeCell ref="A43:P43"/>
     <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
